--- a/docs/go_live_task_ledger_utf8.xlsx
+++ b/docs/go_live_task_ledger_utf8.xlsx
@@ -2417,7 +2417,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TaskLedgerTable" displayName="TaskLedgerTable" ref="A1:L79">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L79" etc:filterBottomFollowUsedRange="0"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L79" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="未完成"/>
+        <filter val="部分完成"/>
+        <filter val="待环境验证"/>
+        <filter val="待人工回归"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" name="任务ID"/>
     <tableColumn id="2" name="一级模块"/>
@@ -2775,7 +2784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="43.2" spans="1:12">
+    <row r="2" ht="43.2" hidden="1" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -2889,7 +2898,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:12">
+    <row r="5" ht="28.8" hidden="1" spans="1:12">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -3003,7 +3012,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" ht="43.2" spans="1:12">
+    <row r="8" ht="43.2" hidden="1" spans="1:12">
       <c r="A8" s="2" t="s">
         <v>66</v>
       </c>
@@ -3041,7 +3050,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:12">
+    <row r="9" ht="28.8" hidden="1" spans="1:12">
       <c r="A9" s="2" t="s">
         <v>74</v>
       </c>
@@ -3079,7 +3088,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:12">
+    <row r="10" ht="28.8" hidden="1" spans="1:12">
       <c r="A10" s="2" t="s">
         <v>82</v>
       </c>
@@ -3155,7 +3164,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:12">
+    <row r="12" ht="28.8" hidden="1" spans="1:12">
       <c r="A12" s="2" t="s">
         <v>98</v>
       </c>
@@ -3193,7 +3202,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:12">
+    <row r="13" ht="28.8" hidden="1" spans="1:12">
       <c r="A13" s="2" t="s">
         <v>103</v>
       </c>
@@ -3231,7 +3240,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:12">
+    <row r="14" ht="28.8" hidden="1" spans="1:12">
       <c r="A14" s="2" t="s">
         <v>109</v>
       </c>
@@ -3269,7 +3278,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" hidden="1" spans="1:12">
       <c r="A15" s="2" t="s">
         <v>115</v>
       </c>
@@ -3383,7 +3392,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:12">
+    <row r="18" ht="28.8" hidden="1" spans="1:12">
       <c r="A18" s="2" t="s">
         <v>134</v>
       </c>
@@ -3497,7 +3506,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:12">
+    <row r="21" ht="28.8" hidden="1" spans="1:12">
       <c r="A21" s="2" t="s">
         <v>153</v>
       </c>
@@ -3535,7 +3544,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:12">
+    <row r="22" ht="28.8" hidden="1" spans="1:12">
       <c r="A22" s="2" t="s">
         <v>159</v>
       </c>
@@ -3687,7 +3696,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="26" ht="28.8" spans="1:12">
+    <row r="26" ht="28.8" hidden="1" spans="1:12">
       <c r="A26" s="2" t="s">
         <v>186</v>
       </c>
@@ -3763,7 +3772,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="28" ht="28.8" spans="1:12">
+    <row r="28" ht="28.8" hidden="1" spans="1:12">
       <c r="A28" s="2" t="s">
         <v>200</v>
       </c>
@@ -3801,7 +3810,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" ht="28.8" spans="1:12">
+    <row r="29" ht="28.8" hidden="1" spans="1:12">
       <c r="A29" s="2" t="s">
         <v>209</v>
       </c>
@@ -3839,7 +3848,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="30" ht="28.8" spans="1:12">
+    <row r="30" ht="28.8" hidden="1" spans="1:12">
       <c r="A30" s="2" t="s">
         <v>216</v>
       </c>
@@ -3953,7 +3962,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" hidden="1" spans="1:12">
       <c r="A33" s="2" t="s">
         <v>237</v>
       </c>
@@ -3991,7 +4000,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="34" ht="28.8" spans="1:12">
+    <row r="34" ht="28.8" hidden="1" spans="1:12">
       <c r="A34" s="2" t="s">
         <v>246</v>
       </c>
@@ -4029,7 +4038,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" ht="28.8" spans="1:12">
+    <row r="35" ht="28.8" hidden="1" spans="1:12">
       <c r="A35" s="2" t="s">
         <v>252</v>
       </c>
@@ -4143,7 +4152,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" hidden="1" spans="1:12">
       <c r="A38" s="2" t="s">
         <v>271</v>
       </c>
@@ -4181,7 +4190,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="39" ht="28.8" spans="1:12">
+    <row r="39" ht="28.8" hidden="1" spans="1:12">
       <c r="A39" s="2" t="s">
         <v>278</v>
       </c>
@@ -4219,7 +4228,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="40" ht="28.8" spans="1:12">
+    <row r="40" ht="28.8" hidden="1" spans="1:12">
       <c r="A40" s="2" t="s">
         <v>282</v>
       </c>
@@ -4257,7 +4266,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="41" ht="28.8" spans="1:12">
+    <row r="41" ht="28.8" hidden="1" spans="1:12">
       <c r="A41" s="2" t="s">
         <v>286</v>
       </c>
@@ -4295,7 +4304,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="42" ht="28.8" spans="1:12">
+    <row r="42" ht="28.8" hidden="1" spans="1:12">
       <c r="A42" s="2" t="s">
         <v>291</v>
       </c>
@@ -4333,7 +4342,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="43" ht="28.8" spans="1:12">
+    <row r="43" ht="28.8" hidden="1" spans="1:12">
       <c r="A43" s="2" t="s">
         <v>296</v>
       </c>
@@ -4371,7 +4380,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="44" ht="28.8" spans="1:12">
+    <row r="44" ht="28.8" hidden="1" spans="1:12">
       <c r="A44" s="2" t="s">
         <v>300</v>
       </c>
@@ -4409,7 +4418,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="45" ht="28.8" spans="1:12">
+    <row r="45" ht="28.8" hidden="1" spans="1:12">
       <c r="A45" s="2" t="s">
         <v>304</v>
       </c>
@@ -4599,7 +4608,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" hidden="1" spans="1:12">
       <c r="A50" s="2" t="s">
         <v>336</v>
       </c>
@@ -4637,7 +4646,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="51" ht="28.8" spans="1:12">
+    <row r="51" ht="28.8" hidden="1" spans="1:12">
       <c r="A51" s="2" t="s">
         <v>341</v>
       </c>
@@ -4675,7 +4684,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="52" ht="43.2" spans="1:12">
+    <row r="52" ht="43.2" hidden="1" spans="1:12">
       <c r="A52" s="2" t="s">
         <v>346</v>
       </c>
@@ -4713,7 +4722,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="53" ht="28.8" spans="1:12">
+    <row r="53" ht="28.8" hidden="1" spans="1:12">
       <c r="A53" s="2" t="s">
         <v>350</v>
       </c>
@@ -4751,7 +4760,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" hidden="1" spans="1:12">
       <c r="A54" s="2" t="s">
         <v>357</v>
       </c>
@@ -4789,7 +4798,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="55" ht="28.8" spans="1:12">
+    <row r="55" ht="28.8" hidden="1" spans="1:12">
       <c r="A55" s="2" t="s">
         <v>362</v>
       </c>
@@ -4827,7 +4836,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="56" ht="28.8" spans="1:12">
+    <row r="56" ht="28.8" hidden="1" spans="1:12">
       <c r="A56" s="2" t="s">
         <v>366</v>
       </c>
@@ -4941,7 +4950,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" hidden="1" spans="1:12">
       <c r="A59" s="2" t="s">
         <v>384</v>
       </c>
@@ -4979,7 +4988,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="60" ht="28.8" spans="1:12">
+    <row r="60" ht="28.8" hidden="1" spans="1:12">
       <c r="A60" s="2" t="s">
         <v>389</v>
       </c>
@@ -5017,7 +5026,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="61" ht="28.8" spans="1:12">
+    <row r="61" ht="28.8" hidden="1" spans="1:12">
       <c r="A61" s="2" t="s">
         <v>395</v>
       </c>
@@ -5169,7 +5178,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="65" ht="28.8" spans="1:12">
+    <row r="65" ht="28.8" hidden="1" spans="1:12">
       <c r="A65" s="2" t="s">
         <v>420</v>
       </c>
@@ -5207,7 +5216,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="66" ht="28.8" spans="1:12">
+    <row r="66" ht="28.8" hidden="1" spans="1:12">
       <c r="A66" s="2" t="s">
         <v>427</v>
       </c>
@@ -5397,7 +5406,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="71" ht="28.8" spans="1:12">
+    <row r="71" ht="28.8" hidden="1" spans="1:12">
       <c r="A71" s="2" t="s">
         <v>455</v>
       </c>
@@ -5663,7 +5672,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" hidden="1" spans="1:12">
       <c r="A78" s="2" t="s">
         <v>503</v>
       </c>
@@ -5701,7 +5710,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" hidden="1" spans="1:12">
       <c r="A79" s="2" t="s">
         <v>510</v>
       </c>
